--- a/artfynd/A 49774-2025 artfynd.xlsx
+++ b/artfynd/A 49774-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133659059</v>
+        <v>133659515</v>
       </c>
       <c r="B3" t="n">
         <v>99181</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483602</v>
+        <v>483697</v>
       </c>
       <c r="R3" t="n">
-        <v>6844532</v>
+        <v>6844579</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,19 +866,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133659515</v>
+        <v>133659059</v>
       </c>
       <c r="B4" t="n">
         <v>99181</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483697</v>
+        <v>483602</v>
       </c>
       <c r="R4" t="n">
-        <v>6844579</v>
+        <v>6844532</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,19 +972,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133659856</v>
+        <v>133659795</v>
       </c>
       <c r="B5" t="n">
         <v>99181</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483690</v>
+        <v>483689</v>
       </c>
       <c r="R5" t="n">
-        <v>6844656</v>
+        <v>6844645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133659795</v>
+        <v>133659856</v>
       </c>
       <c r="B6" t="n">
         <v>99181</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483689</v>
+        <v>483690</v>
       </c>
       <c r="R6" t="n">
-        <v>6844645</v>
+        <v>6844656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133658974</v>
+        <v>133659179</v>
       </c>
       <c r="B7" t="n">
         <v>99181</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483591</v>
+        <v>483619</v>
       </c>
       <c r="R7" t="n">
-        <v>6844519</v>
+        <v>6844513</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133659179</v>
+        <v>133657940</v>
       </c>
       <c r="B8" t="n">
         <v>99181</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483619</v>
+        <v>483657</v>
       </c>
       <c r="R8" t="n">
-        <v>6844513</v>
+        <v>6844579</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133657940</v>
+        <v>133658974</v>
       </c>
       <c r="B9" t="n">
         <v>99181</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483657</v>
+        <v>483591</v>
       </c>
       <c r="R9" t="n">
-        <v>6844579</v>
+        <v>6844519</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133659093</v>
+        <v>133660436</v>
       </c>
       <c r="B13" t="n">
         <v>99181</v>
@@ -1842,26 +1842,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483613</v>
+        <v>483850</v>
       </c>
       <c r="R13" t="n">
-        <v>6844523</v>
+        <v>6844631</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1911,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133660436</v>
+        <v>133659093</v>
       </c>
       <c r="B14" t="n">
         <v>99181</v>
@@ -1948,17 +1939,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483850</v>
+        <v>483613</v>
       </c>
       <c r="R14" t="n">
-        <v>6844631</v>
+        <v>6844523</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133658956</v>
+        <v>133660433</v>
       </c>
       <c r="B19" t="n">
         <v>99181</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483577</v>
+        <v>483842</v>
       </c>
       <c r="R19" t="n">
-        <v>6844530</v>
+        <v>6844628</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,69 +2526,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133660433</v>
+        <v>133658198</v>
       </c>
       <c r="B20" t="n">
-        <v>99181</v>
+        <v>79391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483842</v>
+        <v>483637</v>
       </c>
       <c r="R20" t="n">
-        <v>6844628</v>
+        <v>6844588</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2750,48 +2741,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133658198</v>
+        <v>133658956</v>
       </c>
       <c r="B22" t="n">
-        <v>79391</v>
+        <v>99181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483637</v>
+        <v>483577</v>
       </c>
       <c r="R22" t="n">
-        <v>6844588</v>
+        <v>6844530</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133659408</v>
+        <v>133659815</v>
       </c>
       <c r="B23" t="n">
         <v>99181</v>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483682</v>
+        <v>483730</v>
       </c>
       <c r="R23" t="n">
-        <v>6844532</v>
+        <v>6844628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,57 +2941,66 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133660337</v>
+        <v>133658773</v>
       </c>
       <c r="B24" t="n">
-        <v>80368</v>
+        <v>99181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483755</v>
+        <v>483565</v>
       </c>
       <c r="R24" t="n">
-        <v>6844683</v>
+        <v>6844554</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,54 +3059,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133658773</v>
+        <v>133660337</v>
       </c>
       <c r="B25" t="n">
-        <v>99181</v>
+        <v>80368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483565</v>
+        <v>483755</v>
       </c>
       <c r="R25" t="n">
-        <v>6844554</v>
+        <v>6844683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133659815</v>
+        <v>133659408</v>
       </c>
       <c r="B26" t="n">
         <v>99181</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483730</v>
+        <v>483682</v>
       </c>
       <c r="R26" t="n">
-        <v>6844628</v>
+        <v>6844532</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,12 +3250,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3359,7 +3359,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133658339</v>
+        <v>133658322</v>
       </c>
       <c r="B28" t="n">
         <v>99181</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483494</v>
+        <v>483622</v>
       </c>
       <c r="R28" t="n">
-        <v>6844544</v>
+        <v>6844574</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3453,19 +3453,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133660593</v>
+        <v>133659624</v>
       </c>
       <c r="B29" t="n">
         <v>99181</v>
@@ -3493,20 +3493,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483894</v>
+        <v>483704</v>
       </c>
       <c r="R29" t="n">
-        <v>6844588</v>
+        <v>6844582</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3550,12 +3559,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3668,7 +3677,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133658322</v>
+        <v>133658339</v>
       </c>
       <c r="B31" t="n">
         <v>99181</v>
@@ -3698,7 +3707,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3712,13 +3721,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483622</v>
+        <v>483494</v>
       </c>
       <c r="R31" t="n">
-        <v>6844574</v>
+        <v>6844544</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3762,19 +3771,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133659624</v>
+        <v>133660593</v>
       </c>
       <c r="B32" t="n">
         <v>99181</v>
@@ -3802,29 +3811,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483704</v>
+        <v>483894</v>
       </c>
       <c r="R32" t="n">
-        <v>6844582</v>
+        <v>6844588</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3868,69 +3868,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133658892</v>
+        <v>133660459</v>
       </c>
       <c r="B33" t="n">
-        <v>99181</v>
+        <v>58349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483563</v>
+        <v>483850</v>
       </c>
       <c r="R33" t="n">
-        <v>6844537</v>
+        <v>6844631</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3986,48 +3977,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133660459</v>
+        <v>133658488</v>
       </c>
       <c r="B34" t="n">
-        <v>58349</v>
+        <v>99181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483850</v>
+        <v>483494</v>
       </c>
       <c r="R34" t="n">
-        <v>6844631</v>
+        <v>6844565</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133658488</v>
+        <v>133658892</v>
       </c>
       <c r="B35" t="n">
         <v>99181</v>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483494</v>
+        <v>483563</v>
       </c>
       <c r="R35" t="n">
-        <v>6844565</v>
+        <v>6844537</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4189,45 +4189,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133660292</v>
+        <v>133658485</v>
       </c>
       <c r="B36" t="n">
-        <v>80368</v>
+        <v>99181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483779</v>
+        <v>483565</v>
       </c>
       <c r="R36" t="n">
-        <v>6844656</v>
+        <v>6844530</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4286,54 +4295,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133658485</v>
+        <v>133660292</v>
       </c>
       <c r="B37" t="n">
-        <v>99181</v>
+        <v>80368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483565</v>
+        <v>483779</v>
       </c>
       <c r="R37" t="n">
-        <v>6844530</v>
+        <v>6844656</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133660002</v>
+        <v>133658451</v>
       </c>
       <c r="B39" t="n">
         <v>99181</v>
@@ -4526,17 +4526,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483682</v>
+        <v>483489</v>
       </c>
       <c r="R39" t="n">
-        <v>6844671</v>
+        <v>6844548</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4595,7 +4604,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133658451</v>
+        <v>133660002</v>
       </c>
       <c r="B40" t="n">
         <v>99181</v>
@@ -4623,26 +4632,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483489</v>
+        <v>483682</v>
       </c>
       <c r="R40" t="n">
-        <v>6844548</v>
+        <v>6844671</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133660161</v>
+        <v>133660492</v>
       </c>
       <c r="B41" t="n">
         <v>99181</v>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483755</v>
+        <v>483869</v>
       </c>
       <c r="R41" t="n">
-        <v>6844683</v>
+        <v>6844614</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4795,19 +4795,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133660492</v>
+        <v>133660161</v>
       </c>
       <c r="B42" t="n">
         <v>99181</v>
@@ -4851,13 +4851,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483869</v>
+        <v>483755</v>
       </c>
       <c r="R42" t="n">
-        <v>6844614</v>
+        <v>6844683</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4901,12 +4901,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5226,7 +5226,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133658377</v>
+        <v>133657822</v>
       </c>
       <c r="B46" t="n">
         <v>99181</v>
@@ -5254,20 +5254,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483498</v>
+        <v>483652</v>
       </c>
       <c r="R46" t="n">
-        <v>6844552</v>
+        <v>6844561</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5311,19 +5320,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133657822</v>
+        <v>133658377</v>
       </c>
       <c r="B47" t="n">
         <v>99181</v>
@@ -5351,29 +5360,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483652</v>
+        <v>483498</v>
       </c>
       <c r="R47" t="n">
-        <v>6844561</v>
+        <v>6844552</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5623,7 +5623,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134347734</v>
+        <v>134351319</v>
       </c>
       <c r="B50" t="n">
         <v>99181</v>
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483553</v>
+        <v>483646</v>
       </c>
       <c r="R50" t="n">
-        <v>6844503</v>
+        <v>6844610</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,7 +5720,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134351319</v>
+        <v>134347734</v>
       </c>
       <c r="B51" t="n">
         <v>99181</v>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483646</v>
+        <v>483553</v>
       </c>
       <c r="R51" t="n">
-        <v>6844610</v>
+        <v>6844503</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 49774-2025 artfynd.xlsx
+++ b/artfynd/A 49774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133660490</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133659515</v>
+        <v>133659059</v>
       </c>
       <c r="B3" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483697</v>
+        <v>483602</v>
       </c>
       <c r="R3" t="n">
-        <v>6844579</v>
+        <v>6844532</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +866,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133659059</v>
+        <v>133659515</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483602</v>
+        <v>483697</v>
       </c>
       <c r="R4" t="n">
-        <v>6844532</v>
+        <v>6844579</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,12 +972,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -987,7 +987,7 @@
         <v>133659795</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>133659856</v>
       </c>
       <c r="B6" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,57 +1196,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133659179</v>
+        <v>133658237</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483619</v>
+        <v>483532</v>
       </c>
       <c r="R7" t="n">
-        <v>6844513</v>
+        <v>6844515</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,22 +1281,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133657940</v>
+        <v>133658974</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,7 +1323,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1346,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483657</v>
+        <v>483591</v>
       </c>
       <c r="R8" t="n">
-        <v>6844579</v>
+        <v>6844519</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1408,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133658974</v>
+        <v>133659179</v>
       </c>
       <c r="B9" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1429,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1452,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483591</v>
+        <v>483619</v>
       </c>
       <c r="R9" t="n">
-        <v>6844519</v>
+        <v>6844513</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1514,48 +1505,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133658237</v>
+        <v>133657940</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483532</v>
+        <v>483657</v>
       </c>
       <c r="R10" t="n">
-        <v>6844515</v>
+        <v>6844579</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,12 +1599,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
         <v>133660114</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>133659569</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>133660436</v>
       </c>
       <c r="B13" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>133659093</v>
       </c>
       <c r="B14" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>133657898</v>
       </c>
       <c r="B15" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133659208</v>
+        <v>133659173</v>
       </c>
       <c r="B16" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483634</v>
+        <v>483624</v>
       </c>
       <c r="R16" t="n">
-        <v>6844503</v>
+        <v>6844507</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2217,57 +2217,66 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133658807</v>
+        <v>133659208</v>
       </c>
       <c r="B17" t="n">
-        <v>79391</v>
+        <v>99188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483570</v>
+        <v>483634</v>
       </c>
       <c r="R17" t="n">
-        <v>6844542</v>
+        <v>6844503</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2326,57 +2335,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133659173</v>
+        <v>133658807</v>
       </c>
       <c r="B18" t="n">
-        <v>99181</v>
+        <v>79398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483624</v>
+        <v>483570</v>
       </c>
       <c r="R18" t="n">
-        <v>6844507</v>
+        <v>6844542</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2420,22 +2420,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133660433</v>
+        <v>133658956</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483842</v>
+        <v>483577</v>
       </c>
       <c r="R19" t="n">
-        <v>6844628</v>
+        <v>6844530</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,57 +2526,66 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133658198</v>
+        <v>133659914</v>
       </c>
       <c r="B20" t="n">
-        <v>79391</v>
+        <v>99188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483637</v>
+        <v>483740</v>
       </c>
       <c r="R20" t="n">
-        <v>6844588</v>
+        <v>6844662</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2635,54 +2644,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133659914</v>
+        <v>133658198</v>
       </c>
       <c r="B21" t="n">
-        <v>99181</v>
+        <v>79398</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483740</v>
+        <v>483637</v>
       </c>
       <c r="R21" t="n">
-        <v>6844662</v>
+        <v>6844588</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133658956</v>
+        <v>133660433</v>
       </c>
       <c r="B22" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483577</v>
+        <v>483842</v>
       </c>
       <c r="R22" t="n">
-        <v>6844530</v>
+        <v>6844628</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2835,22 +2835,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133659815</v>
+        <v>133659408</v>
       </c>
       <c r="B23" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483730</v>
+        <v>483682</v>
       </c>
       <c r="R23" t="n">
-        <v>6844628</v>
+        <v>6844532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,66 +2941,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133658773</v>
+        <v>133660337</v>
       </c>
       <c r="B24" t="n">
-        <v>99181</v>
+        <v>80375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483565</v>
+        <v>483755</v>
       </c>
       <c r="R24" t="n">
-        <v>6844554</v>
+        <v>6844683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,45 +3050,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133660337</v>
+        <v>133658773</v>
       </c>
       <c r="B25" t="n">
-        <v>80368</v>
+        <v>99188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483755</v>
+        <v>483565</v>
       </c>
       <c r="R25" t="n">
-        <v>6844683</v>
+        <v>6844554</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133659408</v>
+        <v>133659815</v>
       </c>
       <c r="B26" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483682</v>
+        <v>483730</v>
       </c>
       <c r="R26" t="n">
-        <v>6844532</v>
+        <v>6844628</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,12 +3250,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
         <v>133659684</v>
       </c>
       <c r="B27" t="n">
-        <v>80368</v>
+        <v>80375</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>133658322</v>
       </c>
       <c r="B28" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133659624</v>
+        <v>133660593</v>
       </c>
       <c r="B29" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,29 +3493,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483704</v>
+        <v>483894</v>
       </c>
       <c r="R29" t="n">
-        <v>6844582</v>
+        <v>6844588</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3559,12 +3550,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3574,7 +3565,7 @@
         <v>133660526</v>
       </c>
       <c r="B30" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,7 +3671,7 @@
         <v>133658339</v>
       </c>
       <c r="B31" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3783,10 +3774,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133660593</v>
+        <v>133659624</v>
       </c>
       <c r="B32" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3811,20 +3802,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483894</v>
+        <v>483704</v>
       </c>
       <c r="R32" t="n">
-        <v>6844588</v>
+        <v>6844582</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3868,12 +3868,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
         <v>133658488</v>
       </c>
       <c r="B34" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>133658892</v>
       </c>
       <c r="B35" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>133658485</v>
       </c>
       <c r="B36" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>133660292</v>
       </c>
       <c r="B37" t="n">
-        <v>80368</v>
+        <v>80375</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133659855</v>
+        <v>133658451</v>
       </c>
       <c r="B38" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4436,13 +4436,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483734</v>
+        <v>483489</v>
       </c>
       <c r="R38" t="n">
-        <v>6844644</v>
+        <v>6844548</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4486,22 +4486,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133658451</v>
+        <v>133659855</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483489</v>
+        <v>483734</v>
       </c>
       <c r="R39" t="n">
-        <v>6844548</v>
+        <v>6844644</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4592,12 +4592,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
         <v>133660002</v>
       </c>
       <c r="B40" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,10 +4701,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133660492</v>
+        <v>133660161</v>
       </c>
       <c r="B41" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483869</v>
+        <v>483755</v>
       </c>
       <c r="R41" t="n">
-        <v>6844614</v>
+        <v>6844683</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4795,22 +4795,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133660161</v>
+        <v>133660492</v>
       </c>
       <c r="B42" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,13 +4851,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483755</v>
+        <v>483869</v>
       </c>
       <c r="R42" t="n">
-        <v>6844683</v>
+        <v>6844614</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4901,12 +4901,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4916,7 +4916,7 @@
         <v>133659229</v>
       </c>
       <c r="B43" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>133659679</v>
       </c>
       <c r="B44" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>133660544</v>
       </c>
       <c r="B45" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133657822</v>
+        <v>133658377</v>
       </c>
       <c r="B46" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5254,29 +5254,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483652</v>
+        <v>483498</v>
       </c>
       <c r="R46" t="n">
-        <v>6844561</v>
+        <v>6844552</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5320,22 +5311,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133658377</v>
+        <v>133657822</v>
       </c>
       <c r="B47" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5360,20 +5351,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483498</v>
+        <v>483652</v>
       </c>
       <c r="R47" t="n">
-        <v>6844552</v>
+        <v>6844561</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5432,7 +5432,7 @@
         <v>134348344</v>
       </c>
       <c r="B48" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>134347936</v>
       </c>
       <c r="B49" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>134351319</v>
       </c>
       <c r="B50" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>134347734</v>
       </c>
       <c r="B51" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>134347910</v>
       </c>
       <c r="B52" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>134348035</v>
       </c>
       <c r="B53" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>134348297</v>
       </c>
       <c r="B54" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>134347897</v>
       </c>
       <c r="B55" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>134347977</v>
       </c>
       <c r="B56" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>134351379</v>
       </c>
       <c r="B57" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>134348227</v>
       </c>
       <c r="B58" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>134348201</v>
       </c>
       <c r="B59" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>134348285</v>
       </c>
       <c r="B60" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>134348319</v>
       </c>
       <c r="B61" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 49774-2025 artfynd.xlsx
+++ b/artfynd/A 49774-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133660490</v>
+        <v>133658198</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483873</v>
+        <v>483637</v>
       </c>
       <c r="R2" t="n">
-        <v>6844632</v>
+        <v>6844588</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,69 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133659059</v>
+        <v>133658807</v>
       </c>
       <c r="B3" t="n">
-        <v>99188</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483602</v>
+        <v>483570</v>
       </c>
       <c r="R3" t="n">
-        <v>6844532</v>
+        <v>6844542</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133659515</v>
+        <v>133658237</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,46 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483697</v>
+        <v>483532</v>
       </c>
       <c r="R4" t="n">
-        <v>6844579</v>
+        <v>6844515</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,69 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133659795</v>
+        <v>133659684</v>
       </c>
       <c r="B5" t="n">
-        <v>99188</v>
+        <v>80382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483689</v>
+        <v>483718</v>
       </c>
       <c r="R5" t="n">
-        <v>6844645</v>
+        <v>6844599</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,69 +1051,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133659856</v>
+        <v>133660292</v>
       </c>
       <c r="B6" t="n">
-        <v>99188</v>
+        <v>80382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483690</v>
+        <v>483779</v>
       </c>
       <c r="R6" t="n">
         <v>6844656</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133658237</v>
+        <v>133657565</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>58349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483532</v>
+        <v>483697</v>
       </c>
       <c r="R7" t="n">
-        <v>6844515</v>
+        <v>6844473</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1293,57 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133658974</v>
+        <v>133660459</v>
       </c>
       <c r="B8" t="n">
-        <v>99188</v>
+        <v>58349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483591</v>
+        <v>483850</v>
       </c>
       <c r="R8" t="n">
-        <v>6844519</v>
+        <v>6844631</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,69 +1342,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133659179</v>
+        <v>134348201</v>
       </c>
       <c r="B9" t="n">
-        <v>99188</v>
+        <v>99099</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483619</v>
+        <v>483423</v>
       </c>
       <c r="R9" t="n">
-        <v>6844513</v>
+        <v>6844648</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1473,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133657940</v>
+        <v>133657822</v>
       </c>
       <c r="B10" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483657</v>
+        <v>483652</v>
       </c>
       <c r="R10" t="n">
-        <v>6844579</v>
+        <v>6844561</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1611,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133660114</v>
+        <v>133657826</v>
       </c>
       <c r="B11" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,17 +1585,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483714</v>
+        <v>483694</v>
       </c>
       <c r="R11" t="n">
-        <v>6844687</v>
+        <v>6844479</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133659569</v>
+        <v>133657898</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1693,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1752,13 +1707,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483707</v>
+        <v>483665</v>
       </c>
       <c r="R12" t="n">
-        <v>6844582</v>
+        <v>6844588</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,22 +1757,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133660436</v>
+        <v>133657940</v>
       </c>
       <c r="B13" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,20 +1797,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483850</v>
+        <v>483657</v>
       </c>
       <c r="R13" t="n">
-        <v>6844631</v>
+        <v>6844579</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,22 +1863,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133659093</v>
+        <v>133658322</v>
       </c>
       <c r="B14" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1905,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1955,13 +1919,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483613</v>
+        <v>483622</v>
       </c>
       <c r="R14" t="n">
-        <v>6844523</v>
+        <v>6844574</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,22 +1969,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133657898</v>
+        <v>133658339</v>
       </c>
       <c r="B15" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,7 +2011,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2061,13 +2025,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483665</v>
+        <v>483494</v>
       </c>
       <c r="R15" t="n">
-        <v>6844588</v>
+        <v>6844544</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2111,22 +2075,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133659173</v>
+        <v>133658377</v>
       </c>
       <c r="B16" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,29 +2115,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483624</v>
+        <v>483498</v>
       </c>
       <c r="R16" t="n">
-        <v>6844507</v>
+        <v>6844552</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2229,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133659208</v>
+        <v>133658451</v>
       </c>
       <c r="B17" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2214,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2273,13 +2228,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483634</v>
+        <v>483489</v>
       </c>
       <c r="R17" t="n">
-        <v>6844503</v>
+        <v>6844548</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2323,57 +2278,66 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133658807</v>
+        <v>133658485</v>
       </c>
       <c r="B18" t="n">
-        <v>79398</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483570</v>
+        <v>483565</v>
       </c>
       <c r="R18" t="n">
-        <v>6844542</v>
+        <v>6844530</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2432,10 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133658956</v>
+        <v>133658488</v>
       </c>
       <c r="B19" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2426,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2476,13 +2440,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483577</v>
+        <v>483494</v>
       </c>
       <c r="R19" t="n">
-        <v>6844530</v>
+        <v>6844565</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,10 +2502,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133659914</v>
+        <v>133658773</v>
       </c>
       <c r="B20" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,13 +2546,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483740</v>
+        <v>483565</v>
       </c>
       <c r="R20" t="n">
-        <v>6844662</v>
+        <v>6844554</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,60 +2596,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133658198</v>
+        <v>133658892</v>
       </c>
       <c r="B21" t="n">
-        <v>79398</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483637</v>
+        <v>483563</v>
       </c>
       <c r="R21" t="n">
-        <v>6844588</v>
+        <v>6844537</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,22 +2702,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133660433</v>
+        <v>133658956</v>
       </c>
       <c r="B22" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2744,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2785,13 +2758,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483842</v>
+        <v>483577</v>
       </c>
       <c r="R22" t="n">
-        <v>6844628</v>
+        <v>6844530</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2835,22 +2808,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133659408</v>
+        <v>133658974</v>
       </c>
       <c r="B23" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2850,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2891,13 +2864,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483682</v>
+        <v>483591</v>
       </c>
       <c r="R23" t="n">
-        <v>6844532</v>
+        <v>6844519</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2941,57 +2914,66 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133660337</v>
+        <v>133659059</v>
       </c>
       <c r="B24" t="n">
-        <v>80375</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483755</v>
+        <v>483602</v>
       </c>
       <c r="R24" t="n">
-        <v>6844683</v>
+        <v>6844532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,10 +3032,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133658773</v>
+        <v>133659093</v>
       </c>
       <c r="B25" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,7 +3062,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3094,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483565</v>
+        <v>483613</v>
       </c>
       <c r="R25" t="n">
-        <v>6844554</v>
+        <v>6844523</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3156,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133659815</v>
+        <v>133659173</v>
       </c>
       <c r="B26" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,7 +3168,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3200,10 +3182,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483730</v>
+        <v>483624</v>
       </c>
       <c r="R26" t="n">
-        <v>6844628</v>
+        <v>6844507</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,57 +3232,66 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133659684</v>
+        <v>133659179</v>
       </c>
       <c r="B27" t="n">
-        <v>80375</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483718</v>
+        <v>483619</v>
       </c>
       <c r="R27" t="n">
-        <v>6844599</v>
+        <v>6844513</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3359,10 +3350,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133658322</v>
+        <v>133659208</v>
       </c>
       <c r="B28" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3403,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483622</v>
+        <v>483634</v>
       </c>
       <c r="R28" t="n">
-        <v>6844574</v>
+        <v>6844503</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3465,10 +3456,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133660593</v>
+        <v>133659229</v>
       </c>
       <c r="B29" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,20 +3484,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483894</v>
+        <v>483647</v>
       </c>
       <c r="R29" t="n">
-        <v>6844588</v>
+        <v>6844509</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3562,10 +3557,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133660526</v>
+        <v>133659408</v>
       </c>
       <c r="B30" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,17 +3597,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483888</v>
+        <v>483682</v>
       </c>
       <c r="R30" t="n">
-        <v>6844638</v>
+        <v>6844532</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3668,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133658339</v>
+        <v>133659515</v>
       </c>
       <c r="B31" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3712,13 +3707,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483494</v>
+        <v>483697</v>
       </c>
       <c r="R31" t="n">
-        <v>6844544</v>
+        <v>6844579</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3762,22 +3757,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133659624</v>
+        <v>133659569</v>
       </c>
       <c r="B32" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3799,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3818,13 +3813,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483704</v>
+        <v>483707</v>
       </c>
       <c r="R32" t="n">
         <v>6844582</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3868,60 +3863,69 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133660459</v>
+        <v>133659624</v>
       </c>
       <c r="B33" t="n">
-        <v>58349</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483850</v>
+        <v>483704</v>
       </c>
       <c r="R33" t="n">
-        <v>6844631</v>
+        <v>6844582</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3965,22 +3969,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133658488</v>
+        <v>133659679</v>
       </c>
       <c r="B34" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4007,7 +4011,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4021,13 +4025,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483494</v>
+        <v>483689</v>
       </c>
       <c r="R34" t="n">
-        <v>6844565</v>
+        <v>6844616</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4083,10 +4087,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133658892</v>
+        <v>133659795</v>
       </c>
       <c r="B35" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,7 +4117,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4127,10 +4131,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483563</v>
+        <v>483689</v>
       </c>
       <c r="R35" t="n">
-        <v>6844537</v>
+        <v>6844645</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4189,10 +4193,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133658485</v>
+        <v>133659815</v>
       </c>
       <c r="B36" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4219,7 +4223,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4233,13 +4237,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483565</v>
+        <v>483730</v>
       </c>
       <c r="R36" t="n">
-        <v>6844530</v>
+        <v>6844628</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4295,48 +4299,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133660292</v>
+        <v>133659855</v>
       </c>
       <c r="B37" t="n">
-        <v>80375</v>
+        <v>99195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483779</v>
+        <v>483734</v>
       </c>
       <c r="R37" t="n">
-        <v>6844656</v>
+        <v>6844644</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4392,10 +4405,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133658451</v>
+        <v>133659856</v>
       </c>
       <c r="B38" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4435,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4436,10 +4449,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483489</v>
+        <v>483690</v>
       </c>
       <c r="R38" t="n">
-        <v>6844548</v>
+        <v>6844656</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4498,10 +4511,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133659855</v>
+        <v>133660433</v>
       </c>
       <c r="B39" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,7 +4541,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4542,10 +4555,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483734</v>
+        <v>483842</v>
       </c>
       <c r="R39" t="n">
-        <v>6844644</v>
+        <v>6844628</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4604,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133660002</v>
+        <v>133660436</v>
       </c>
       <c r="B40" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4635,14 +4648,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483682</v>
+        <v>483850</v>
       </c>
       <c r="R40" t="n">
-        <v>6844671</v>
+        <v>6844631</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,10 +4714,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133660161</v>
+        <v>133660490</v>
       </c>
       <c r="B41" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4729,26 +4742,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483755</v>
+        <v>483873</v>
       </c>
       <c r="R41" t="n">
-        <v>6844683</v>
+        <v>6844632</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,7 +4814,7 @@
         <v>133660492</v>
       </c>
       <c r="B42" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4913,10 +4917,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133659229</v>
+        <v>133660526</v>
       </c>
       <c r="B43" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4943,22 +4947,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483647</v>
+        <v>483888</v>
       </c>
       <c r="R43" t="n">
-        <v>6844509</v>
+        <v>6844638</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5014,10 +5023,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133659679</v>
+        <v>133660544</v>
       </c>
       <c r="B44" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5053,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5054,17 +5063,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483689</v>
+        <v>483891</v>
       </c>
       <c r="R44" t="n">
-        <v>6844616</v>
+        <v>6844625</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5120,10 +5129,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133660544</v>
+        <v>133660593</v>
       </c>
       <c r="B45" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5148,29 +5157,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483891</v>
+        <v>483894</v>
       </c>
       <c r="R45" t="n">
-        <v>6844625</v>
+        <v>6844588</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133658377</v>
+        <v>134347734</v>
       </c>
       <c r="B46" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5261,13 +5261,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483498</v>
+        <v>483553</v>
       </c>
       <c r="R46" t="n">
-        <v>6844552</v>
+        <v>6844503</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5291,12 +5291,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5323,10 +5323,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133657822</v>
+        <v>134347897</v>
       </c>
       <c r="B47" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5351,29 +5351,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483652</v>
+        <v>483494</v>
       </c>
       <c r="R47" t="n">
-        <v>6844561</v>
+        <v>6844527</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5397,12 +5388,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5417,60 +5408,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134348344</v>
+        <v>134347910</v>
       </c>
       <c r="B48" t="n">
-        <v>99210</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483389</v>
+        <v>483484</v>
       </c>
       <c r="R48" t="n">
-        <v>6844666</v>
+        <v>6844524</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5529,7 +5520,7 @@
         <v>134347936</v>
       </c>
       <c r="B49" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5623,10 +5614,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134351319</v>
+        <v>134347977</v>
       </c>
       <c r="B50" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5658,10 +5649,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483646</v>
+        <v>483469</v>
       </c>
       <c r="R50" t="n">
-        <v>6844610</v>
+        <v>6844539</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134347734</v>
+        <v>134348035</v>
       </c>
       <c r="B51" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5755,13 +5746,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483553</v>
+        <v>483458</v>
       </c>
       <c r="R51" t="n">
-        <v>6844503</v>
+        <v>6844556</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5817,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134347910</v>
+        <v>134351319</v>
       </c>
       <c r="B52" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5852,13 +5843,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483484</v>
+        <v>483646</v>
       </c>
       <c r="R52" t="n">
-        <v>6844524</v>
+        <v>6844610</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5914,10 +5905,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134348035</v>
+        <v>134351379</v>
       </c>
       <c r="B53" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,13 +5940,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483458</v>
+        <v>483646</v>
       </c>
       <c r="R53" t="n">
-        <v>6844556</v>
+        <v>6844602</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6011,10 +6002,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134348297</v>
+        <v>134348227</v>
       </c>
       <c r="B54" t="n">
-        <v>99210</v>
+        <v>99217</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6046,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483404</v>
+        <v>483419</v>
       </c>
       <c r="R54" t="n">
-        <v>6844662</v>
+        <v>6844649</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6108,45 +6099,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134347897</v>
+        <v>134348319</v>
       </c>
       <c r="B55" t="n">
-        <v>99188</v>
+        <v>99217</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483494</v>
+        <v>483385</v>
       </c>
       <c r="R55" t="n">
-        <v>6844527</v>
+        <v>6844654</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6205,32 +6196,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134347977</v>
+        <v>133660337</v>
       </c>
       <c r="B56" t="n">
-        <v>99188</v>
+        <v>80382</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6240,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483469</v>
+        <v>483755</v>
       </c>
       <c r="R56" t="n">
-        <v>6844539</v>
+        <v>6844683</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6270,12 +6261,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6302,45 +6293,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134351379</v>
+        <v>134348285</v>
       </c>
       <c r="B57" t="n">
-        <v>99188</v>
+        <v>99099</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fallnäset, Fallnäset, Dlr</t>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483646</v>
+        <v>483404</v>
       </c>
       <c r="R57" t="n">
-        <v>6844602</v>
+        <v>6844662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6399,48 +6390,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134348227</v>
+        <v>133659914</v>
       </c>
       <c r="B58" t="n">
-        <v>99210</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483419</v>
+        <v>483740</v>
       </c>
       <c r="R58" t="n">
-        <v>6844649</v>
+        <v>6844662</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6484,57 +6484,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134348201</v>
+        <v>133660002</v>
       </c>
       <c r="B59" t="n">
-        <v>99092</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483423</v>
+        <v>483682</v>
       </c>
       <c r="R59" t="n">
-        <v>6844648</v>
+        <v>6844671</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6593,45 +6593,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134348285</v>
+        <v>133660114</v>
       </c>
       <c r="B60" t="n">
-        <v>99092</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483404</v>
+        <v>483714</v>
       </c>
       <c r="R60" t="n">
-        <v>6844662</v>
+        <v>6844687</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6690,45 +6690,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134348319</v>
+        <v>133660161</v>
       </c>
       <c r="B61" t="n">
-        <v>99210</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+          <t>Fallnäset, Fallnäset, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483385</v>
+        <v>483755</v>
       </c>
       <c r="R61" t="n">
-        <v>6844654</v>
+        <v>6844683</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6755,12 +6764,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6784,6 +6793,297 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134348258</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>483409</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6844663</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134348297</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>483404</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6844662</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134348344</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fallnäsudden, Fallnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>483389</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6844666</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
